--- a/ChatBI业务元数据_光峰财务管理.xlsx
+++ b/ChatBI业务元数据_光峰财务管理.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">活动!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">业务对象!$A$1:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">逻辑实体!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">业务属性!$A$1:$J$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">业务属性!$A$1:$J$163</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">实体关系!$A$1:$H$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">指标!$A$1:$Q$17</definedName>
   </definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2662" uniqueCount="1036">
   <si>
     <t>术语编码</t>
   </si>
@@ -2339,9 +2339,6 @@
     <t>AT00243</t>
   </si>
   <si>
-    <t>FMaterialCode</t>
-  </si>
-  <si>
     <t>AT00244</t>
   </si>
   <si>
@@ -2385,6 +2382,54 @@
   </si>
   <si>
     <t>FChecker</t>
+  </si>
+  <si>
+    <t>AT00249</t>
+  </si>
+  <si>
+    <t>AT00250</t>
+  </si>
+  <si>
+    <t>AT00251</t>
+  </si>
+  <si>
+    <t>AT00252</t>
+  </si>
+  <si>
+    <t>AT00253</t>
+  </si>
+  <si>
+    <t>AT00254</t>
+  </si>
+  <si>
+    <t>AT00255</t>
+  </si>
+  <si>
+    <t>库存分类</t>
+  </si>
+  <si>
+    <t>FStockCategory</t>
+  </si>
+  <si>
+    <t>AT00256</t>
+  </si>
+  <si>
+    <t>AT00257</t>
+  </si>
+  <si>
+    <t>AT00258</t>
+  </si>
+  <si>
+    <t>AT00259</t>
+  </si>
+  <si>
+    <t>AT00260</t>
+  </si>
+  <si>
+    <t>AT00261</t>
+  </si>
+  <si>
+    <t>AT00262</t>
   </si>
   <si>
     <t>关系编号</t>
@@ -3120,7 +3165,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3190,12 +3235,6 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3350,7 +3389,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3372,6 +3411,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3731,13 +3776,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3746,122 +3794,119 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3936,22 +3981,25 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3983,7 +4031,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4010,58 +4058,57 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0"/>
-    <cellStyle name="千位分隔" xfId="1"/>
-    <cellStyle name="货币" xfId="2"/>
-    <cellStyle name="百分比" xfId="3"/>
-    <cellStyle name="千位分隔[0]" xfId="4"/>
-    <cellStyle name="货币[0]" xfId="5"/>
-    <cellStyle name="超链接" xfId="6"/>
-    <cellStyle name="已访问的超链接" xfId="7"/>
-    <cellStyle name="注释" xfId="8"/>
-    <cellStyle name="警告文本" xfId="9"/>
-    <cellStyle name="标题" xfId="10"/>
-    <cellStyle name="解释性文本" xfId="11"/>
-    <cellStyle name="标题 1" xfId="12"/>
-    <cellStyle name="标题 2" xfId="13"/>
-    <cellStyle name="标题 3" xfId="14"/>
-    <cellStyle name="标题 4" xfId="15"/>
-    <cellStyle name="输入" xfId="16"/>
-    <cellStyle name="输出" xfId="17"/>
-    <cellStyle name="计算" xfId="18"/>
-    <cellStyle name="检查单元格" xfId="19"/>
-    <cellStyle name="链接单元格" xfId="20"/>
-    <cellStyle name="汇总" xfId="21"/>
-    <cellStyle name="好" xfId="22"/>
-    <cellStyle name="差" xfId="23"/>
-    <cellStyle name="适中" xfId="24"/>
-    <cellStyle name="强调文字颜色 1" xfId="25"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <cellStyle name="强调文字颜色 2" xfId="29"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <cellStyle name="强调文字颜色 3" xfId="33"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <cellStyle name="强调文字颜色 4" xfId="37"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <cellStyle name="强调文字颜色 5" xfId="41"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <cellStyle name="强调文字颜色 6" xfId="45"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4075,7 +4122,7 @@
 <file path=xl/woinfos.xml><?xml version="1.0" encoding="utf-8"?>
 <woInfos xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookInfo cellCmpFml="0" dbFileVersion="0">
-    <open main="35" threadCnt="1"/>
+    <open main="33" threadCnt="1"/>
     <sheetInfos>
       <sheetInfo cellCmpFml="0" sheetStid="1">
         <open threadCnt="1"/>
@@ -4093,7 +4140,7 @@
         <open threadCnt="1"/>
       </sheetInfo>
       <sheetInfo cellCmpFml="0" sheetStid="6">
-        <open main="1" threadCnt="1"/>
+        <open main="2" threadCnt="1"/>
       </sheetInfo>
       <sheetInfo cellCmpFml="0" sheetStid="7">
         <open threadCnt="1"/>
@@ -4399,7 +4446,7 @@
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="26" style="51" customWidth="1"/>
+    <col min="4" max="4" width="26" style="54" customWidth="1"/>
     <col min="5" max="5" width="52" customWidth="1"/>
     <col min="6" max="7" width="12" style="3" customWidth="1"/>
   </cols>
@@ -4437,7 +4484,7 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="D2" s="55" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -4458,7 +4505,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="55" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -4481,7 +4528,7 @@
       <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="55" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -4502,7 +4549,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="55" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -4525,7 +4572,7 @@
       <c r="C6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="55" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -4548,7 +4595,7 @@
       <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="55" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -4571,7 +4618,7 @@
       <c r="C8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="55" t="s">
         <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -4592,7 +4639,7 @@
         <v>48</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="55" t="s">
         <v>49</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -4615,7 +4662,7 @@
       <c r="C10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -4638,7 +4685,7 @@
       <c r="C11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="55" t="s">
         <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -4661,7 +4708,7 @@
       <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="55" t="s">
         <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -4684,7 +4731,7 @@
       <c r="C13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="55" t="s">
         <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -4707,7 +4754,7 @@
       <c r="C14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="55" t="s">
         <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -4730,7 +4777,7 @@
       <c r="C15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="55" t="s">
         <v>81</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -4753,7 +4800,7 @@
       <c r="C16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="55" t="s">
         <v>86</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -4776,7 +4823,7 @@
       <c r="C17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="55" t="s">
         <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -4799,7 +4846,7 @@
       <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="55" t="s">
         <v>97</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -4822,7 +4869,7 @@
       <c r="C19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="55" t="s">
         <v>102</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -4845,7 +4892,7 @@
       <c r="C20" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="55" t="s">
         <v>108</v>
       </c>
       <c r="E20" s="2" t="s">
@@ -4868,7 +4915,7 @@
       <c r="C21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="55" t="s">
         <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -4891,7 +4938,7 @@
       <c r="C22" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="52" t="s">
+      <c r="D22" s="55" t="s">
         <v>119</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -4914,7 +4961,7 @@
       <c r="C23" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="55" t="s">
         <v>124</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -4937,7 +4984,7 @@
       <c r="C24" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="55" t="s">
         <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -4958,7 +5005,7 @@
         <v>132</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -4979,7 +5026,7 @@
         <v>137</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="55" t="s">
         <v>138</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -5002,7 +5049,7 @@
       <c r="C27" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="55" t="s">
         <v>143</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -5025,7 +5072,7 @@
       <c r="C28" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="55" t="s">
         <v>148</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -5048,7 +5095,7 @@
       <c r="C29" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="55" t="s">
         <v>153</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -5071,7 +5118,7 @@
       <c r="C30" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="55" t="s">
         <v>158</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -5094,7 +5141,7 @@
       <c r="C31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="55" t="s">
         <v>163</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -5117,7 +5164,7 @@
       <c r="C32" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="55" t="s">
         <v>168</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -5140,7 +5187,7 @@
       <c r="C33" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="55" t="s">
         <v>173</v>
       </c>
       <c r="E33" s="2" t="s">
@@ -5161,7 +5208,7 @@
         <v>176</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="55" t="s">
         <v>177</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -5184,7 +5231,7 @@
       <c r="C35" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="55" t="s">
         <v>182</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -5207,7 +5254,7 @@
       <c r="C36" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D36" s="52" t="s">
+      <c r="D36" s="55" t="s">
         <v>188</v>
       </c>
       <c r="E36" s="2" t="s">
@@ -5230,7 +5277,7 @@
       <c r="C37" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="52" t="s">
+      <c r="D37" s="55" t="s">
         <v>193</v>
       </c>
       <c r="E37" s="2" t="s">
@@ -5251,7 +5298,7 @@
         <v>196</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="55" t="s">
         <v>197</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -5272,7 +5319,7 @@
         <v>200</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="52" t="s">
+      <c r="D39" s="55" t="s">
         <v>201</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -5293,7 +5340,7 @@
         <v>204</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="52" t="s">
+      <c r="D40" s="55" t="s">
         <v>205</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -5316,7 +5363,7 @@
       <c r="C41" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="D41" s="55" t="s">
         <v>210</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -5330,93 +5377,93 @@
       </c>
     </row>
     <row r="42" s="15" customFormat="1" ht="27" spans="1:7">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="C42" s="54"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="56" t="s">
+      <c r="C42" s="57"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
     </row>
     <row r="43" s="15" customFormat="1" ht="27" spans="1:7">
-      <c r="A43" s="53" t="s">
+      <c r="A43" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="C43" s="54"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="56" t="s">
+      <c r="C43" s="57"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
     </row>
     <row r="44" s="15" customFormat="1" ht="27" spans="1:7">
-      <c r="A44" s="53" t="s">
+      <c r="A44" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="44" t="s">
+      <c r="B44" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="56" t="s">
+      <c r="C44" s="60"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
     </row>
     <row r="45" s="15" customFormat="1" ht="81" spans="1:7">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="56" t="s">
         <v>221</v>
       </c>
-      <c r="B45" s="58" t="s">
+      <c r="B45" s="61" t="s">
         <v>222</v>
       </c>
-      <c r="C45" s="57"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="56" t="s">
+      <c r="C45" s="60"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
     </row>
     <row r="46" s="15" customFormat="1" spans="1:7">
-      <c r="A46" s="53" t="s">
+      <c r="A46" s="56" t="s">
         <v>224</v>
       </c>
       <c r="B46" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
       <c r="E46" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-    </row>
-    <row r="47" s="16" customFormat="1" spans="1:7">
-      <c r="A47" s="59" t="s">
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+    </row>
+    <row r="47" s="38" customFormat="1" spans="1:7">
+      <c r="A47" s="62" t="s">
         <v>227</v>
       </c>
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="D47" s="60"/>
-      <c r="E47" s="35" t="s">
+      <c r="D47" s="53"/>
+      <c r="E47" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -5680,295 +5727,295 @@
   </cols>
   <sheetData>
     <row r="1" ht="27" spans="1:6">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="44" t="s">
         <v>271</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="43" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="2" ht="40.5" spans="1:6">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="45" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>274</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="45" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="3" ht="27" spans="1:6">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="46" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="45" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="45" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="45" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="5" ht="94.5" spans="1:6">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="45" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="45" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:6">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="45" t="s">
         <v>287</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="45" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="7" ht="40.5" spans="1:6">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="45" t="s">
         <v>289</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="47" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="8" ht="40.5" spans="1:6">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="45" t="s">
         <v>292</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="45" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:6">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="45" t="s">
         <v>295</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="45" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="10" ht="40.5" spans="1:6">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="45" t="s">
         <v>298</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="45" t="s">
         <v>299</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="45" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:6">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="45" t="s">
         <v>301</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="45" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="45" t="s">
         <v>304</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="45" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="45" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:6">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="47" t="s">
         <v>309</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="42" t="s">
+      <c r="C13" s="50"/>
+      <c r="D13" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="42" t="s">
+      <c r="E13" s="50"/>
+      <c r="F13" s="45" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="14" ht="40.5" spans="1:6">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="47" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="42" t="s">
+      <c r="C14" s="50"/>
+      <c r="D14" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="42" t="s">
+      <c r="E14" s="50"/>
+      <c r="F14" s="45" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="15" ht="99.75" spans="1:6">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="47" t="s">
         <v>312</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="49" t="s">
+      <c r="C15" s="50"/>
+      <c r="D15" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="42" t="s">
+      <c r="E15" s="50"/>
+      <c r="F15" s="45" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="47" t="s">
         <v>315</v>
       </c>
       <c r="B16" s="30" t="s">
@@ -5981,19 +6028,19 @@
         <v>316</v>
       </c>
     </row>
-    <row r="17" s="16" customFormat="1" spans="1:6">
-      <c r="A17" s="39" t="s">
+    <row r="17" s="38" customFormat="1" spans="1:6">
+      <c r="A17" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="35" t="s">
+      <c r="C17" s="53"/>
+      <c r="D17" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="35" t="s">
+      <c r="E17" s="53"/>
+      <c r="F17" s="39" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6449,7 +6496,7 @@
       <c r="D19" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="41" t="s">
         <v>385</v>
       </c>
       <c r="F19" s="30" t="s">
@@ -6460,25 +6507,25 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="42" t="s">
         <v>317</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="37" t="s">
         <v>386</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="39" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6495,14 +6542,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="14.625" style="3" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
@@ -10676,299 +10723,705 @@
         <v>406</v>
       </c>
     </row>
-    <row r="140" s="16" customFormat="1" ht="14.25" spans="1:10">
-      <c r="A140" s="32" t="s">
+    <row r="140" s="15" customFormat="1" ht="14.25" spans="1:10">
+      <c r="A140" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B140" s="33" t="s">
+      <c r="B140" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C140" s="33" t="s">
+      <c r="C140" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="D140" s="34" t="s">
+      <c r="D140" s="23" t="s">
         <v>753</v>
       </c>
-      <c r="E140" s="35" t="s">
+      <c r="E140" s="30" t="s">
         <v>754</v>
       </c>
-      <c r="F140" s="36" t="s">
+      <c r="F140" s="31" t="s">
         <v>755</v>
       </c>
-      <c r="G140" s="35" t="s">
+      <c r="G140" s="30" t="s">
         <v>754</v>
       </c>
-      <c r="H140" s="37" t="s">
+      <c r="H140" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="I140" s="37" t="s">
+      <c r="I140" s="28" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="141" s="16" customFormat="1" ht="14.25" spans="1:10">
-      <c r="A141" s="32" t="s">
+    <row r="141" s="15" customFormat="1" ht="14.25" spans="1:10">
+      <c r="A141" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B141" s="33" t="s">
+      <c r="B141" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C141" s="33" t="s">
+      <c r="C141" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="D141" s="34" t="s">
+      <c r="D141" s="23" t="s">
         <v>756</v>
       </c>
-      <c r="E141" s="35" t="s">
+      <c r="E141" s="30" t="s">
         <v>743</v>
       </c>
-      <c r="F141" s="36" t="s">
+      <c r="F141" s="31" t="s">
         <v>744</v>
       </c>
-      <c r="G141" s="37" t="s">
+      <c r="G141" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="H141" s="37" t="s">
+      <c r="H141" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="I141" s="37" t="s">
+      <c r="I141" s="28" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="142" s="16" customFormat="1" ht="14.25" spans="1:10">
-      <c r="A142" s="32" t="s">
+    <row r="142" s="15" customFormat="1" ht="14.25" spans="1:10">
+      <c r="A142" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B142" s="33" t="s">
+      <c r="B142" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C142" s="33" t="s">
+      <c r="C142" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="D142" s="34" t="s">
+      <c r="D142" s="23" t="s">
         <v>757</v>
       </c>
-      <c r="E142" s="35" t="s">
+      <c r="E142" s="30" t="s">
         <v>758</v>
       </c>
-      <c r="F142" s="36" t="s">
+      <c r="F142" s="31" t="s">
         <v>759</v>
       </c>
-      <c r="G142" s="35" t="s">
+      <c r="G142" s="30" t="s">
         <v>758</v>
       </c>
-      <c r="H142" s="37" t="s">
+      <c r="H142" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="I142" s="37" t="s">
+      <c r="I142" s="28" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="143" s="16" customFormat="1" ht="14.25" spans="1:10">
-      <c r="A143" s="32" t="s">
+    <row r="143" s="15" customFormat="1" ht="14.25" spans="1:10">
+      <c r="A143" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B143" s="33" t="s">
+      <c r="B143" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C143" s="33" t="s">
+      <c r="C143" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="D143" s="34" t="s">
+      <c r="D143" s="23" t="s">
         <v>760</v>
       </c>
-      <c r="E143" s="35" t="s">
+      <c r="E143" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="F143" s="36" t="s">
+      <c r="F143" s="31" t="s">
         <v>762</v>
       </c>
-      <c r="G143" s="35" t="s">
+      <c r="G143" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="H143" s="37" t="s">
+      <c r="H143" s="28" t="s">
         <v>516</v>
       </c>
-      <c r="I143" s="37" t="s">
+      <c r="I143" s="28" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="144" s="16" customFormat="1" ht="14.25" spans="1:10">
-      <c r="A144" s="32" t="s">
+    <row r="144" s="15" customFormat="1" ht="14.25" spans="1:10">
+      <c r="A144" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B144" s="33" t="s">
+      <c r="B144" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="C144" s="33" t="s">
+      <c r="C144" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="D144" s="34" t="s">
+      <c r="D144" s="23" t="s">
         <v>763</v>
       </c>
-      <c r="E144" s="35" t="s">
+      <c r="E144" s="30" t="s">
         <v>444</v>
       </c>
-      <c r="F144" s="36" t="s">
+      <c r="F144" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="G144" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="H144" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="I144" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="145" s="15" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A145" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C145" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D145" s="23" t="s">
         <v>764</v>
       </c>
-      <c r="G144" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="H144" s="37" t="s">
+      <c r="E145" s="30" t="s">
+        <v>765</v>
+      </c>
+      <c r="F145" s="31" t="s">
+        <v>766</v>
+      </c>
+      <c r="G145" s="30" t="s">
+        <v>765</v>
+      </c>
+      <c r="H145" s="28" t="s">
+        <v>447</v>
+      </c>
+      <c r="I145" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="146" s="15" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A146" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C146" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D146" s="23" t="s">
+        <v>767</v>
+      </c>
+      <c r="E146" s="30" t="s">
+        <v>768</v>
+      </c>
+      <c r="F146" s="31" t="s">
+        <v>769</v>
+      </c>
+      <c r="G146" s="30" t="s">
+        <v>768</v>
+      </c>
+      <c r="H146" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="I146" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="147" s="15" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A147" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D147" s="23" t="s">
+        <v>770</v>
+      </c>
+      <c r="E147" s="30" t="s">
+        <v>771</v>
+      </c>
+      <c r="F147" s="31" t="s">
+        <v>772</v>
+      </c>
+      <c r="G147" s="30" t="s">
+        <v>771</v>
+      </c>
+      <c r="H147" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="I147" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" s="15" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A148" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B148" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D148" s="23" t="s">
+        <v>773</v>
+      </c>
+      <c r="E148" s="30" t="s">
+        <v>774</v>
+      </c>
+      <c r="F148" s="31" t="s">
+        <v>775</v>
+      </c>
+      <c r="G148" s="30" t="s">
+        <v>774</v>
+      </c>
+      <c r="H148" s="28" t="s">
+        <v>465</v>
+      </c>
+      <c r="I148" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="149" s="15" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A149" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B149" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="D149" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="E149" s="30" t="s">
+        <v>777</v>
+      </c>
+      <c r="F149" s="31" t="s">
+        <v>778</v>
+      </c>
+      <c r="G149" s="30" t="s">
+        <v>777</v>
+      </c>
+      <c r="H149" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="I149" s="28" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" s="16" customFormat="1" spans="1:9">
+      <c r="A150" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="B150" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C150" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="D150" s="33" t="s">
+        <v>779</v>
+      </c>
+      <c r="E150" s="36" t="s">
+        <v>718</v>
+      </c>
+      <c r="F150" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="G150" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="I150" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="151" s="16" customFormat="1" spans="1:9">
+      <c r="A151" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="B151" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C151" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="D151" s="33" t="s">
+        <v>780</v>
+      </c>
+      <c r="E151" s="36" t="s">
+        <v>718</v>
+      </c>
+      <c r="F151" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="G151" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="H151" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="I151" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="152" s="16" customFormat="1" spans="1:9">
+      <c r="A152" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B152" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="C152" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="D152" s="33" t="s">
+        <v>781</v>
+      </c>
+      <c r="E152" s="36" t="s">
+        <v>718</v>
+      </c>
+      <c r="F152" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="G152" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="H152" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="I152" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="153" s="16" customFormat="1" spans="1:9">
+      <c r="A153" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="C153" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="D153" s="33" t="s">
+        <v>782</v>
+      </c>
+      <c r="E153" s="36" t="s">
+        <v>718</v>
+      </c>
+      <c r="F153" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="G153" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="H153" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="I153" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="154" s="16" customFormat="1" spans="1:9">
+      <c r="A154" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="B154" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C154" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="D154" s="33" t="s">
+        <v>783</v>
+      </c>
+      <c r="E154" s="36" t="s">
+        <v>718</v>
+      </c>
+      <c r="F154" s="36" t="s">
+        <v>719</v>
+      </c>
+      <c r="G154" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="H154" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="I154" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="155" s="16" customFormat="1" spans="1:9">
+      <c r="A155" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B155" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="C155" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="D155" s="33" t="s">
+        <v>784</v>
+      </c>
+      <c r="E155" s="38" t="s">
+        <v>718</v>
+      </c>
+      <c r="F155" s="38" t="s">
+        <v>719</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="H155" s="38" t="s">
+        <v>452</v>
+      </c>
+      <c r="I155" s="38" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="156" s="16" customFormat="1" spans="1:9">
+      <c r="A156" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="B156" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C156" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="D156" s="33" t="s">
+        <v>785</v>
+      </c>
+      <c r="E156" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F156" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G156" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H156" s="36" t="s">
         <v>400</v>
       </c>
-      <c r="I144" s="37" t="s">
+      <c r="I156" s="36" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="145" s="16" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A145" s="32" t="s">
+    <row r="157" s="16" customFormat="1" spans="1:9">
+      <c r="A157" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="B157" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C157" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="D157" s="33" t="s">
+        <v>788</v>
+      </c>
+      <c r="E157" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F157" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G157" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H157" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I157" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="158" s="16" customFormat="1" spans="1:9">
+      <c r="A158" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C158" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="D158" s="33" t="s">
+        <v>789</v>
+      </c>
+      <c r="E158" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F158" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G158" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H158" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I158" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" s="16" customFormat="1" spans="1:9">
+      <c r="A159" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B159" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="C159" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="D159" s="33" t="s">
+        <v>790</v>
+      </c>
+      <c r="E159" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F159" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G159" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H159" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I159" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="160" s="16" customFormat="1" spans="1:9">
+      <c r="A160" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B160" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="C160" s="35" t="s">
+        <v>378</v>
+      </c>
+      <c r="D160" s="33" t="s">
+        <v>791</v>
+      </c>
+      <c r="E160" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F160" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G160" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H160" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I160" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="161" s="16" customFormat="1" spans="1:9">
+      <c r="A161" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="B161" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C161" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="D161" s="33" t="s">
+        <v>792</v>
+      </c>
+      <c r="E161" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F161" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G161" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H161" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I161" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="162" s="16" customFormat="1" spans="1:9">
+      <c r="A162" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="B162" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C162" s="40" t="s">
+        <v>385</v>
+      </c>
+      <c r="D162" s="33" t="s">
+        <v>793</v>
+      </c>
+      <c r="E162" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F162" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G162" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H162" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I162" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="163" s="16" customFormat="1" spans="1:9">
+      <c r="A163" s="37" t="s">
         <v>386</v>
       </c>
-      <c r="B145" s="33" t="s">
+      <c r="B163" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="C145" s="33" t="s">
+      <c r="C163" s="34" t="s">
         <v>387</v>
       </c>
-      <c r="D145" s="34" t="s">
-        <v>765</v>
-      </c>
-      <c r="E145" s="35" t="s">
-        <v>766</v>
-      </c>
-      <c r="F145" s="36" t="s">
-        <v>767</v>
-      </c>
-      <c r="G145" s="35" t="s">
-        <v>766</v>
-      </c>
-      <c r="H145" s="37" t="s">
-        <v>447</v>
-      </c>
-      <c r="I145" s="37" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="146" s="16" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A146" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B146" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C146" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="D146" s="34" t="s">
-        <v>768</v>
-      </c>
-      <c r="E146" s="35" t="s">
-        <v>769</v>
-      </c>
-      <c r="F146" s="36" t="s">
-        <v>770</v>
-      </c>
-      <c r="G146" s="35" t="s">
-        <v>769</v>
-      </c>
-      <c r="H146" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="I146" s="37" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="147" s="16" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A147" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B147" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C147" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="D147" s="34" t="s">
-        <v>771</v>
-      </c>
-      <c r="E147" s="35" t="s">
-        <v>772</v>
-      </c>
-      <c r="F147" s="36" t="s">
-        <v>773</v>
-      </c>
-      <c r="G147" s="35" t="s">
-        <v>772</v>
-      </c>
-      <c r="H147" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="I147" s="37" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="148" s="16" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A148" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B148" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C148" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="D148" s="34" t="s">
-        <v>774</v>
-      </c>
-      <c r="E148" s="35" t="s">
-        <v>775</v>
-      </c>
-      <c r="F148" s="36" t="s">
-        <v>776</v>
-      </c>
-      <c r="G148" s="35" t="s">
-        <v>775</v>
-      </c>
-      <c r="H148" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="I148" s="37" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="149" s="16" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A149" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="B149" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C149" s="33" t="s">
-        <v>387</v>
-      </c>
-      <c r="D149" s="34" t="s">
-        <v>777</v>
-      </c>
-      <c r="E149" s="35" t="s">
-        <v>778</v>
-      </c>
-      <c r="F149" s="36" t="s">
-        <v>779</v>
-      </c>
-      <c r="G149" s="35" t="s">
-        <v>778</v>
-      </c>
-      <c r="H149" s="37" t="s">
-        <v>452</v>
-      </c>
-      <c r="I149" s="37" t="s">
+      <c r="D163" s="33" t="s">
+        <v>794</v>
+      </c>
+      <c r="E163" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="F163" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="G163" s="39" t="s">
+        <v>786</v>
+      </c>
+      <c r="H163" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="I163" s="36" t="s">
         <v>406</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J149" etc:filterBottomFollowUsedRange="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J163" etc:filterBottomFollowUsedRange="1">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10993,33 +11446,33 @@
   <sheetData>
     <row r="1" ht="27" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
     </row>
     <row r="2" ht="27" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>323</v>
@@ -11034,18 +11487,18 @@
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3" ht="27" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>323</v>
@@ -11060,10 +11513,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>398</v>
@@ -11071,7 +11524,7 @@
     </row>
     <row r="4" ht="27" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>329</v>
@@ -11086,10 +11539,10 @@
         <v>180</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>441</v>
@@ -11097,7 +11550,7 @@
     </row>
     <row r="5" ht="27" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>323</v>
@@ -11112,10 +11565,10 @@
         <v>180</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>398</v>
@@ -11123,7 +11576,7 @@
     </row>
     <row r="6" ht="27" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>333</v>
@@ -11138,10 +11591,10 @@
         <v>186</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>472</v>
@@ -11149,7 +11602,7 @@
     </row>
     <row r="7" ht="27" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>323</v>
@@ -11164,10 +11617,10 @@
         <v>186</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>398</v>
@@ -11175,7 +11628,7 @@
     </row>
     <row r="8" ht="27" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>333</v>
@@ -11187,13 +11640,13 @@
         <v>349</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>472</v>
@@ -11201,7 +11654,7 @@
     </row>
     <row r="9" ht="27" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>323</v>
@@ -11213,13 +11666,13 @@
         <v>349</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>398</v>
@@ -11227,13 +11680,13 @@
     </row>
     <row r="10" ht="27" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>349</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>353</v>
@@ -11242,10 +11695,10 @@
         <v>354</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>533</v>
@@ -11253,7 +11706,7 @@
     </row>
     <row r="11" ht="27" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>329</v>
@@ -11268,10 +11721,10 @@
         <v>354</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>441</v>
@@ -11279,7 +11732,7 @@
     </row>
     <row r="12" ht="27" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>326</v>
@@ -11294,10 +11747,10 @@
         <v>354</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>427</v>
@@ -11305,7 +11758,7 @@
     </row>
     <row r="13" ht="27" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>336</v>
@@ -11317,13 +11770,13 @@
         <v>358</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>487</v>
@@ -11331,13 +11784,13 @@
     </row>
     <row r="14" ht="27" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>358</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>362</v>
@@ -11346,10 +11799,10 @@
         <v>363</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>533</v>
@@ -11357,7 +11810,7 @@
     </row>
     <row r="15" ht="27" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>329</v>
@@ -11372,10 +11825,10 @@
         <v>363</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>441</v>
@@ -11383,7 +11836,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>329</v>
@@ -11395,13 +11848,13 @@
         <v>367</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>441</v>
@@ -11409,7 +11862,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>329</v>
@@ -11424,10 +11877,10 @@
         <v>213</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>441</v>
@@ -11435,7 +11888,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>329</v>
@@ -11450,10 +11903,10 @@
         <v>80</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>441</v>
@@ -11461,7 +11914,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>323</v>
@@ -11476,10 +11929,10 @@
         <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>398</v>
@@ -11487,7 +11940,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>329</v>
@@ -11499,13 +11952,13 @@
         <v>373</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>441</v>
@@ -11513,7 +11966,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>323</v>
@@ -11525,13 +11978,13 @@
         <v>373</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>398</v>
@@ -11539,7 +11992,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>329</v>
@@ -11554,10 +12007,10 @@
         <v>216</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>441</v>
@@ -11565,7 +12018,7 @@
     </row>
     <row r="23" s="6" customFormat="1" spans="1:8">
       <c r="A23" s="9" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>323</v>
@@ -11580,13 +12033,13 @@
         <v>219</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -11625,78 +12078,78 @@
   <sheetData>
     <row r="1" ht="27" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>859</v>
+        <v>874</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="H2" s="5">
         <v>2</v>
@@ -11709,7 +12162,7 @@
         <v>615</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="2"/>
@@ -11719,22 +12172,22 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="5">
@@ -11748,7 +12201,7 @@
         <v>612</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="2"/>
@@ -11758,25 +12211,25 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>636</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="H4" s="5">
         <v>2</v>
@@ -11789,7 +12242,7 @@
         <v>635</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="2"/>
@@ -11799,22 +12252,22 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>644</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="5">
@@ -11828,7 +12281,7 @@
         <v>643</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="2"/>
@@ -11838,22 +12291,22 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>632</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="5">
@@ -11867,7 +12320,7 @@
         <v>631</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="2"/>
@@ -11877,22 +12330,22 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>640</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="5">
@@ -11906,7 +12359,7 @@
         <v>639</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="2"/>
@@ -11916,31 +12369,31 @@
     </row>
     <row r="8" ht="27" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -11953,25 +12406,25 @@
     </row>
     <row r="9" ht="27" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="H9" s="5">
         <v>2</v>
@@ -11984,7 +12437,7 @@
         <v>561</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="2"/>
@@ -11996,22 +12449,22 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="5">
@@ -12025,7 +12478,7 @@
         <v>557</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="2"/>
@@ -12037,22 +12490,22 @@
     </row>
     <row r="11" ht="27" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="5">
@@ -12066,11 +12519,11 @@
         <v>561</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -12078,29 +12531,29 @@
     </row>
     <row r="12" ht="27" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="5">
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -12113,22 +12566,22 @@
     </row>
     <row r="13" ht="27" spans="1:17">
       <c r="A13" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>927</v>
+        <v>942</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>929</v>
+        <v>944</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>930</v>
+        <v>945</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="5">
@@ -12142,11 +12595,11 @@
         <v>561</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M13" s="5"/>
       <c r="N13" s="2" t="s">
-        <v>931</v>
+        <v>946</v>
       </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -12154,22 +12607,22 @@
     </row>
     <row r="14" ht="27" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>932</v>
+        <v>947</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>934</v>
+        <v>949</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>935</v>
+        <v>950</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>936</v>
+        <v>951</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>937</v>
+        <v>952</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="5">
@@ -12183,11 +12636,11 @@
         <v>561</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="2" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -12195,22 +12648,22 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="2" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>940</v>
+        <v>955</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>941</v>
+        <v>956</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>942</v>
+        <v>957</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>943</v>
+        <v>958</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>357</v>
@@ -12226,7 +12679,7 @@
         <v>561</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="2"/>
@@ -12236,22 +12689,22 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="2" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>946</v>
+        <v>961</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>201</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>949</v>
+        <v>964</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="5">
@@ -12265,7 +12718,7 @@
         <v>563</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="2"/>
@@ -12275,22 +12728,22 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="2" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>205</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="5">
@@ -12304,7 +12757,7 @@
         <v>565</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="2"/>
@@ -12341,16 +12794,16 @@
   <sheetData>
     <row r="1" ht="27" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>15</v>
@@ -12368,7 +12821,7 @@
         <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>657</v>
@@ -12380,10 +12833,10 @@
         <v>675</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>479</v>
@@ -12391,28 +12844,28 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -12423,28 +12876,28 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="2" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -12455,26 +12908,26 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -12485,19 +12938,19 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -12513,19 +12966,19 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="2" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -12541,16 +12994,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="2" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -12567,16 +13020,16 @@
     </row>
     <row r="8" ht="27" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -12593,115 +13046,115 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="2" t="s">
-        <v>975</v>
+        <v>990</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="2" t="s">
-        <v>977</v>
+        <v>992</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>978</v>
+        <v>993</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
-        <v>979</v>
+        <v>994</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>980</v>
+        <v>995</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="2" t="s">
-        <v>981</v>
+        <v>996</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>982</v>
+        <v>997</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -12709,31 +13162,31 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>983</v>
+        <v>998</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -12741,27 +13194,27 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>985</v>
+        <v>1000</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>986</v>
+        <v>1001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -12772,26 +13225,26 @@
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>987</v>
+        <v>1002</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>988</v>
+        <v>1003</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -12805,21 +13258,21 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>989</v>
+        <v>1004</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>990</v>
+        <v>1005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -12833,21 +13286,21 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="2" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -12861,16 +13314,16 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="2" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -12887,16 +13340,16 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="2" t="s">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -12913,16 +13366,16 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="2" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>998</v>
+        <v>1013</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -12939,20 +13392,20 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="2" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -12967,20 +13420,20 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="2" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -12995,20 +13448,20 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="2" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>636</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -13023,20 +13476,20 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="2" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>644</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -13051,18 +13504,18 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>632</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -13077,18 +13530,18 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>640</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -13103,20 +13556,20 @@
     </row>
     <row r="27" ht="27" spans="1:16">
       <c r="A27" s="2" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -13131,27 +13584,27 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -13161,27 +13614,27 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="2" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -13191,20 +13644,20 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="2" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -13212,10 +13665,10 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -13223,16 +13676,16 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="2" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -13249,20 +13702,20 @@
     </row>
     <row r="32" ht="27" spans="1:16">
       <c r="A32" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -13270,10 +13723,10 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -13281,20 +13734,20 @@
     </row>
     <row r="33" ht="27" spans="1:16">
       <c r="A33" s="2" t="s">
-        <v>932</v>
+        <v>947</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -13302,10 +13755,10 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -13313,20 +13766,20 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="2" t="s">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -13334,7 +13787,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -13343,16 +13796,16 @@
     </row>
     <row r="35" ht="27" spans="1:16">
       <c r="A35" s="2" t="s">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1002</v>
+        <v>1017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -13369,16 +13822,16 @@
     </row>
     <row r="36" ht="27" spans="1:16">
       <c r="A36" s="2" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -13395,16 +13848,16 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="2" t="s">
-        <v>1005</v>
+        <v>1020</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1006</v>
+        <v>1021</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -13421,16 +13874,16 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="2" t="s">
-        <v>1007</v>
+        <v>1022</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1008</v>
+        <v>1023</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -13447,16 +13900,16 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="2" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1010</v>
+        <v>1025</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -13473,16 +13926,16 @@
     </row>
     <row r="40" ht="27" spans="1:16">
       <c r="A40" s="2" t="s">
-        <v>1011</v>
+        <v>1026</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1012</v>
+        <v>1027</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -13499,19 +13952,19 @@
     </row>
     <row r="41" ht="27" spans="1:16">
       <c r="A41" s="2" t="s">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1014</v>
+        <v>1029</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -13527,16 +13980,16 @@
     </row>
     <row r="42" ht="27" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -13553,22 +14006,22 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>1017</v>
+        <v>1032</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>1018</v>
+        <v>1033</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -13581,22 +14034,22 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>1019</v>
+        <v>1034</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -13609,25 +14062,25 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>940</v>
+        <v>955</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -13638,27 +14091,27 @@
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>946</v>
+        <v>961</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -13673,22 +14126,22 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
